--- a/center_first_element_0deg.xlsx
+++ b/center_first_element_0deg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113C1C0A-FCFF-4806-8B9C-05E41551EDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9709C6B-658E-45B6-B660-17AF00372306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{934E2846-E07B-884A-9144-F9B94297545B}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>AoA = 4.75 deg</t>
+    <t>AoA = 6.1 deg</t>
   </si>
 </sst>
 </file>
@@ -579,27 +579,1878 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>center_first_element!$A$1:$A$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="162"/>
+                <c:pt idx="0">
+                  <c:v>1.0002798500000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99928435999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99022144999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97401959999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.95781777000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94180164</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.92578550000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.90784536999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.88835262999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.87233649999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.85824436999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.84241394999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.82658352000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.80727647999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.78623114000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.76866241000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.74606446999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.72520483000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.70608349999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.68870047000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.67653235</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.66436423</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.65064350999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.63499877999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.62283065999999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.60737163000000005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.58843601000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.57279128000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.55559395</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.54013493000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5229376</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.50574028000000004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.48506632999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.46613071</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.44719508000000002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.43347436</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.41280043</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.39560308999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.37666746000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.35773182999999997</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.33879620999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.32141317000000003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.30403014</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.29186202</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.27447899999999997</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.25554336</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.24337523999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.22773051999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.21034748</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.19991766999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.18427294</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.17191912000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1614893</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.14913547999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.13504335000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.12442783</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.11381231</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9.6057870000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>8.5256650000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7.4269719999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6.5206810000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.4405580000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.5156950000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.7646640000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2.9950620000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2.051629E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1.474428E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9.1579599999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.9385399999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2.64313E-3</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2.08603E-3</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.71462E-3</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.3432100000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.8611000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2.2900000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1.4101999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.3296999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7.2491999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1.0168699999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1.327389E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1.6379089999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1.9484290000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2.258949E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2.7432999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>3.0538200000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>3.5381700000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.0225209999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.8545320000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.686542E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6.3632939999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>7.1953050000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7.872055E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>8.8778969999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.10076138</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.11448211</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.12472622</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.13844695000000001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.14869106000000001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.15893518000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.16936498999999999</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.17979481</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.19003892999999999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.20046874000000001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.20916025999999999</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.22132837999999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.23349650999999999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.24566462</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.25609443999999998</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.26652426000000001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.27695407999999999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.29259879999999999</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.30669092999999997</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.31885904999999998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.33121286999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.34338099999999999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.35225821000000002</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.36268802999999999</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.37156525000000001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.38373337000000002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.39608719999999997</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.41017932000000001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.42253313999999997</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.43662527000000001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.44916478999999998</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.45959461000000001</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.47021013</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.48082564999999999</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.49317947000000001</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.50745731000000005</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.51981113000000001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.53235065999999998</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.54644278000000002</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.56072062</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.57673673999999997</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.59082886999999995</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.60336840000000003</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.61398390999999997</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.62478513999999996</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.63713896000000003</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.64967849</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.66221801000000002</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.67301924000000002</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.68903537000000004</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.70523720000000001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.71951503999999999</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.73186885999999995</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.74633238999999996</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.76079591999999996</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.77699775000000004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.79319958999999995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.81287803000000003</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.83274216999999995</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.85260630999999998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.86899384999999996</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.88519568999999998</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.89792090999999996</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.91257014999999997</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.93069599000000003</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.94360692000000002</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.95999445999999999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.97656770000000004</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.99121693</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>center_first_element!$B$1:$B$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="162"/>
+                <c:pt idx="0">
+                  <c:v>2.0677E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.3370199999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7596599999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1630099999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.4336399999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.2926199999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-6.1516100000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.5686599999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.1068450000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.292744E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.322835E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.3349669999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.3471E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.3233139999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.2815679999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.27574E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1.042269E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-8.2675700000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-6.2920399999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-4.4961000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-3.23895E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.9817900000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.19261E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.8089600000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0661100000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.4201199999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.113331E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.274965E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6283249999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.963726E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.317085E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.6704450000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.059723E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.4310420000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.8023609999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.1198020000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.5090810000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4.8624399999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5.2337590000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.6050780000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.976397E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.1559910000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6.3355839999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6.4613000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.6408930000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7.0122130000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7.1379280000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.2995619999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7.4791549999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7.5869110000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7.7485449999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7.7004950000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7.8082499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7.7602000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7.7301090000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7.6640979999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.5980880000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7.4301489999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.1903729999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6.7768300000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6.5190940000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.2793180000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.8478160000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.3983540000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4.7751269999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.1698579999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3.7024380000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3.408783E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2.7496369999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2.246298E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1.7249980000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.3774659999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.0299330000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.0863499999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-1.2663999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-5.51922E-3</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>-1.109139E-2</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>-1.6663569999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>-2.223574E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>-2.607025E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>-2.9904770000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>-3.3739280000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>-3.7573799999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>-4.1587899999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>-4.5422410000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>-4.9436519999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>-5.3450619999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>-5.7823920000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>-6.2197200000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>-6.4653240000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>-6.9026539999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>-7.1482569999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>-7.6035459999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-7.903027E-2</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>-8.2204680000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>-8.5019910000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>-8.8194320000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>-9.100954E-2</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>-9.3824770000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>-9.4902329999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>-9.5979889999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>-9.8795110000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>-9.9872669999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>-0.10077063999999999</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>-0.10202778999999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>-0.10328495</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>-0.10454210999999999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>-0.10561966</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>-0.10669723</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>-0.10777478</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>-0.10939113</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>-0.10909021000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>-0.11034736000000001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>-0.10986686</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>-0.11112402</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>-0.11028432000000001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>-0.11136187</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>-0.11052218</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>-0.11177933</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>-0.11129883</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>-0.11099792</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>-0.1105174</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>-0.11021649</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>-0.10799831999999999</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>-0.10907588</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>-0.10841576999999999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>-0.10775568000000001</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>-0.10727515999999999</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>-0.10523659</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>-0.10475608</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>-0.10253791</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>-0.10223699</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>-0.10019842</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>-9.833944E-2</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>-9.8038520000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>-9.5820349999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>-9.5160239999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>-9.2762490000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>-9.2281970000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>-9.0063809999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>-8.7845629999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>-8.544786E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>-8.3588880000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>-7.9992240000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>-7.7953659999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>-7.7473150000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>-7.3696910000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-6.9920679999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>-6.6324019999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>-6.2727379999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>-5.948991E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>-5.4514800000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>-4.9539680000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>-4.4205359999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>-4.0608720000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>-3.6652879999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>-3.113898E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>-2.598427E-2</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>-2.029077E-2</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>-1.495646E-2</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>-7.8844899999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>-2.3705800000000002E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2B5E-41FA-B072-B335C32A51CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1769389791"/>
+        <c:axId val="1769390271"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1769389791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1769390271"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1769390271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1769389791"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>808789</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>92242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>708525</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>106947</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{924256CC-B24B-86BB-8DEC-815EA02D8353}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>805052</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>121351</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>133684</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>26737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>128441</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>63687</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>793338</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>75511</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F18C7DA6-BDEC-1609-229B-D470F62F42D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A17EB9E4-138C-36E2-71DA-4971A075DEDD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -608,7 +2459,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -621,8 +2472,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2516210" y="722930"/>
-          <a:ext cx="10445915" cy="9567599"/>
+          <a:off x="3556000" y="427790"/>
+          <a:ext cx="8359864" cy="7468247"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -956,10 +2807,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.99999999975571097</v>
+        <v>1.0002798500000001</v>
       </c>
       <c r="B1">
-        <v>8.4359121951220015E-2</v>
+        <v>2.0677E-4</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -967,1290 +2818,1290 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.99824253051142298</v>
+        <v>0.99928435999999998</v>
       </c>
       <c r="B2">
-        <v>9.1382871340392011E-2</v>
+        <v>7.3370199999999997E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.98945518428998191</v>
+        <v>0.99022144999999995</v>
       </c>
       <c r="B3">
-        <v>8.7837020725278006E-2</v>
+        <v>4.7596599999999998E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.973637961091388</v>
+        <v>0.97401959999999999</v>
       </c>
       <c r="B4">
-        <v>8.2508978642462996E-2</v>
+        <v>1.1630099999999999E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.95782073789279398</v>
+        <v>0.95781777000000001</v>
       </c>
       <c r="B5">
-        <v>7.7180936559647015E-2</v>
+        <v>-2.4336399999999999E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.94200351469419996</v>
+        <v>0.94180164</v>
       </c>
       <c r="B6">
-        <v>7.3610376184148993E-2</v>
+        <v>-4.2926199999999996E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.92618629149560594</v>
+        <v>0.92578550000000004</v>
       </c>
       <c r="B7">
-        <v>7.0039815808649999E-2</v>
+        <v>-6.1516100000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.90861159899999999</v>
+        <v>0.90784536999999998</v>
       </c>
       <c r="B8">
-        <v>6.4705596285739006E-2</v>
+        <v>-9.5686599999999997E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.88927943736555293</v>
+        <v>0.88835262999999998</v>
       </c>
       <c r="B9">
-        <v>6.1122681030049017E-2</v>
+        <v>-1.1068450000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.87346221416695891</v>
+        <v>0.87233649999999996</v>
       </c>
       <c r="B10">
-        <v>5.7552120654549996E-2</v>
+        <v>-1.292744E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>0.85940246021265299</v>
+        <v>0.85824436999999998</v>
       </c>
       <c r="B11">
-        <v>5.5745219426465001E-2</v>
+        <v>-1.322835E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.84358523701405896</v>
+        <v>0.84241394999999997</v>
       </c>
       <c r="B12">
-        <v>5.3932140758283995E-2</v>
+        <v>-1.3349669999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.82776801381546494</v>
+        <v>0.82658352000000002</v>
       </c>
       <c r="B13">
-        <v>5.2119062090103016E-2</v>
+        <v>-1.3471E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>0.80843585212829494</v>
+        <v>0.80727647999999996</v>
       </c>
       <c r="B14">
-        <v>5.0293628541730015E-2</v>
+        <v>-1.3233139999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.78734622119683595</v>
+        <v>0.78623114000000005</v>
       </c>
       <c r="B15">
-        <v>4.8462017553260003E-2</v>
+        <v>-1.2815679999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0.76977152875395394</v>
+        <v>0.76866241000000002</v>
       </c>
       <c r="B16">
-        <v>4.6642761444983014E-2</v>
+        <v>-1.27574E-2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>0.74692442857820696</v>
+        <v>0.74606446999999998</v>
       </c>
       <c r="B17">
-        <v>4.6562454723735006E-2</v>
+        <v>-1.042269E-2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.72583479764674796</v>
+        <v>0.72520483000000002</v>
       </c>
       <c r="B18">
-        <v>4.648832544258201E-2</v>
+        <v>-8.2675700000000001E-3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.70650263595957796</v>
+        <v>0.70608349999999998</v>
       </c>
       <c r="B19">
-        <v>4.6420373601525997E-2</v>
+        <v>-6.2920399999999996E-3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0.6889279439999999</v>
+        <v>0.68870047000000001</v>
       </c>
       <c r="B20">
-        <v>4.6358599200565995E-2</v>
+        <v>-4.4961000000000003E-3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>0.67662565880667791</v>
+        <v>0.67653235</v>
       </c>
       <c r="B21">
-        <v>4.6315357119893999E-2</v>
+        <v>-3.23895E-3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.66432337409665998</v>
+        <v>0.66436423</v>
       </c>
       <c r="B22">
-        <v>4.6272115039222003E-2</v>
+        <v>-1.9817900000000002E-3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>0.65026361999999993</v>
+        <v>0.65064350999999998</v>
       </c>
       <c r="B23">
-        <v>4.7980177225771012E-2</v>
+        <v>1.19261E-3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0.63444639699999994</v>
+        <v>0.63499877999999998</v>
       </c>
       <c r="B24">
-        <v>4.7924580264906994E-2</v>
+        <v>2.8089600000000001E-3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.622144112233743</v>
+        <v>0.62283065999999998</v>
       </c>
       <c r="B25">
-        <v>4.7881338184234998E-2</v>
+        <v>4.0661100000000004E-3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>0.60632688903514897</v>
+        <v>0.60737163000000005</v>
       </c>
       <c r="B26">
-        <v>4.9583222930686996E-2</v>
+        <v>7.4201199999999997E-3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.58699472734797797</v>
+        <v>0.58843601000000001</v>
       </c>
       <c r="B27">
-        <v>5.1272752796947998E-2</v>
+        <v>1.113331E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.57117750414938395</v>
+        <v>0.57279128000000001</v>
       </c>
       <c r="B28">
-        <v>5.1217155836084008E-2</v>
+        <v>1.274965E-2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>0.55360281170650194</v>
+        <v>0.55559395</v>
       </c>
       <c r="B29">
-        <v>5.2912863142440994E-2</v>
+        <v>1.6283249999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>0.53778558850790792</v>
+        <v>0.54013493000000001</v>
       </c>
       <c r="B30">
-        <v>5.4614747888893991E-2</v>
+        <v>1.963726E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>0.52021089606502591</v>
+        <v>0.5229376</v>
       </c>
       <c r="B31">
-        <v>5.6310455195251005E-2</v>
+        <v>2.317085E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>0.50263620362214401</v>
+        <v>0.50574028000000004</v>
       </c>
       <c r="B32">
-        <v>5.8006162501607991E-2</v>
+        <v>2.6704450000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>0.48154657269068502</v>
+        <v>0.48506632999999999</v>
       </c>
       <c r="B33">
-        <v>5.968951492777301E-2</v>
+        <v>3.059723E-2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>0.46221441100351501</v>
+        <v>0.46613071</v>
       </c>
       <c r="B34">
-        <v>6.1379044794034013E-2</v>
+        <v>3.4310420000000001E-2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0.44288224931634401</v>
+        <v>0.44719508000000002</v>
       </c>
       <c r="B35">
-        <v>6.3068574660294016E-2</v>
+        <v>3.8023609999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0.42882249536203804</v>
+        <v>0.43347436</v>
       </c>
       <c r="B36">
-        <v>6.4776636846842997E-2</v>
+        <v>4.1198020000000002E-2</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0.40773286443057899</v>
+        <v>0.41280043</v>
       </c>
       <c r="B37">
-        <v>6.6459989273008016E-2</v>
+        <v>4.5090810000000002E-2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>0.39015817198769703</v>
+        <v>0.39560308999999999</v>
       </c>
       <c r="B38">
-        <v>6.8155696579365002E-2</v>
+        <v>4.8624399999999998E-2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0.37082601030052703</v>
+        <v>0.37666746000000001</v>
       </c>
       <c r="B39">
-        <v>6.9845226445626005E-2</v>
+        <v>5.2337590000000003E-2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.35149384861335603</v>
+        <v>0.35773182999999997</v>
       </c>
       <c r="B40">
-        <v>7.1534756311887007E-2</v>
+        <v>5.6050780000000001E-2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.33216168692618603</v>
+        <v>0.33879620999999999</v>
       </c>
       <c r="B41">
-        <v>7.322428617814801E-2</v>
+        <v>5.976397E-2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.31458699400000001</v>
+        <v>0.32141317000000003</v>
       </c>
       <c r="B42">
-        <v>7.3162511777188008E-2</v>
+        <v>6.1559910000000002E-2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>0.29701230204042101</v>
+        <v>0.30403014</v>
       </c>
       <c r="B43">
-        <v>7.3100737376227007E-2</v>
+        <v>6.3355839999999997E-2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0.28471001733040402</v>
+        <v>0.29186202</v>
       </c>
       <c r="B44">
-        <v>7.3057495295555011E-2</v>
+        <v>6.4613000000000004E-2</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.26713532500000003</v>
+        <v>0.27447899999999997</v>
       </c>
       <c r="B45">
-        <v>7.2995720894595009E-2</v>
+        <v>6.6408930000000005E-2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0.24780316320035101</v>
+        <v>0.25554336</v>
       </c>
       <c r="B46">
-        <v>7.4685250760856012E-2</v>
+        <v>7.0122130000000005E-2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>0.23550087849033302</v>
+        <v>0.24337523999999999</v>
       </c>
       <c r="B47">
-        <v>7.4642008680184016E-2</v>
+        <v>7.1379280000000003E-2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.219683655291739</v>
+        <v>0.22773051999999999</v>
       </c>
       <c r="B48">
-        <v>7.4586411719319998E-2</v>
+        <v>7.2995619999999997E-2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.20210896284885702</v>
+        <v>0.21034748</v>
       </c>
       <c r="B49">
-        <v>7.4524637318359996E-2</v>
+        <v>7.4791549999999998E-2</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>0.19156414738312802</v>
+        <v>0.19991766999999999</v>
       </c>
       <c r="B50">
-        <v>7.4487572677783012E-2</v>
+        <v>7.5869110000000003E-2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>0.175746924184534</v>
+        <v>0.18427294</v>
       </c>
       <c r="B51">
-        <v>7.4431975716918994E-2</v>
+        <v>7.7485449999999997E-2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>0.16344463947451601</v>
+        <v>0.17191912000000001</v>
       </c>
       <c r="B52">
-        <v>7.263125192893001E-2</v>
+        <v>7.7004950000000003E-2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>0.15289982400878702</v>
+        <v>0.1614893</v>
       </c>
       <c r="B53">
-        <v>7.2594187288353998E-2</v>
+        <v>7.8082499999999999E-2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>0.140597539298769</v>
+        <v>0.14913547999999999</v>
       </c>
       <c r="B54">
-        <v>7.0793463500365014E-2</v>
+        <v>7.7602000000000004E-2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>0.126537785344463</v>
+        <v>0.13504335000000001</v>
       </c>
       <c r="B55">
-        <v>6.8986562272278992E-2</v>
+        <v>7.7301090000000003E-2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>0.115992969878734</v>
+        <v>0.12442783</v>
       </c>
       <c r="B56">
-        <v>6.7192015924385992E-2</v>
+        <v>7.6640979999999997E-2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>0.10544815441300499</v>
+        <v>0.11381231</v>
       </c>
       <c r="B57">
-        <v>6.5397469576492992E-2</v>
+        <v>7.5980880000000001E-2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>8.7873461999999999E-2</v>
+        <v>9.6057870000000004E-2</v>
       </c>
       <c r="B58">
-        <v>6.1820731760899014E-2</v>
+        <v>7.4301489999999998E-2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>7.7328647E-2</v>
+        <v>8.5256650000000003E-2</v>
       </c>
       <c r="B59">
-        <v>5.8268703705688998E-2</v>
+        <v>7.1903729999999999E-2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>6.6783831000000002E-2</v>
+        <v>7.4269719999999997E-2</v>
       </c>
       <c r="B60">
-        <v>5.2959193943160995E-2</v>
+        <v>6.7768300000000004E-2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>5.7996485E-2</v>
+        <v>6.5206810000000004E-2</v>
       </c>
       <c r="B61">
-        <v>4.9413343328046991E-2</v>
+        <v>6.5190940000000003E-2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>4.7451668999999995E-2</v>
+        <v>5.4405580000000002E-2</v>
       </c>
       <c r="B62">
-        <v>4.5861315272837003E-2</v>
+        <v>6.2793180000000004E-2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>3.8664323E-2</v>
+        <v>4.5156950000000001E-2</v>
       </c>
       <c r="B63">
-        <v>4.055798295040601E-2</v>
+        <v>5.8478160000000001E-2</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>3.1634445999999997E-2</v>
+        <v>3.7646640000000002E-2</v>
       </c>
       <c r="B64">
-        <v>3.5260828068070002E-2</v>
+        <v>5.3983540000000003E-2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>2.4604569175746899E-2</v>
+        <v>2.9950620000000001E-2</v>
       </c>
       <c r="B65">
-        <v>2.8206191478418005E-2</v>
+        <v>4.7751269999999998E-2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1.58172229543058E-2</v>
+        <v>2.051629E-2</v>
       </c>
       <c r="B66">
-        <v>2.1145377448668998E-2</v>
+        <v>4.1698579999999999E-2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>1.0544814999999999E-2</v>
+        <v>1.474428E-2</v>
       </c>
       <c r="B67">
-        <v>1.585440000643E-2</v>
+        <v>3.7024380000000003E-2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>5.2724069999999998E-3</v>
+        <v>9.1579599999999997E-3</v>
       </c>
       <c r="B68">
-        <v>1.232090427150799E-2</v>
+        <v>3.408783E-2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>1.757469E-3</v>
+        <v>4.9385399999999999E-3</v>
       </c>
       <c r="B69">
-        <v>5.2786225620480021E-3</v>
+        <v>2.7496369999999999E-2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>0</v>
+        <v>2.64313E-3</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>2.246298E-2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>0</v>
+        <v>2.08603E-3</v>
       </c>
       <c r="B71">
-        <v>-5.2724451219509916E-3</v>
+        <v>1.7249980000000002E-2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>0</v>
+        <v>1.71462E-3</v>
       </c>
       <c r="B72">
-        <v>-8.7874085365849952E-3</v>
+        <v>1.3774659999999999E-2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>0</v>
+        <v>1.3432100000000001E-3</v>
       </c>
       <c r="B73">
-        <v>-1.2302371951218999E-2</v>
+        <v>1.0299330000000001E-2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>0</v>
+        <v>7.8611000000000002E-4</v>
       </c>
       <c r="B74">
-        <v>-1.757481707316999E-2</v>
+        <v>5.0863499999999999E-3</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>0</v>
+        <v>2.2900000000000001E-4</v>
       </c>
       <c r="B75">
-        <v>-2.2847261950146996E-2</v>
+        <v>-1.2663999999999999E-4</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1.757469E-3</v>
+        <v>1.4101999999999999E-3</v>
       </c>
       <c r="B76">
-        <v>-2.8113529950147001E-2</v>
+        <v>-5.51922E-3</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>5.2724069999999998E-3</v>
+        <v>4.3296999999999997E-3</v>
       </c>
       <c r="B77">
-        <v>-3.3373619950146996E-2</v>
+        <v>-1.109139E-2</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>8.7873459999999997E-3</v>
+        <v>7.2491999999999999E-3</v>
       </c>
       <c r="B78">
-        <v>-3.8633709950146991E-2</v>
+        <v>-1.6663569999999999E-2</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1.2302284465729299E-2</v>
+        <v>1.0168699999999999E-2</v>
       </c>
       <c r="B79">
-        <v>-4.3893800950146999E-2</v>
+        <v>-2.223574E-2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1.58172229543058E-2</v>
+        <v>1.327389E-2</v>
       </c>
       <c r="B80">
-        <v>-4.739640895014699E-2</v>
+        <v>-2.607025E-2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1.9332161E-2</v>
+        <v>1.6379089999999999E-2</v>
       </c>
       <c r="B81">
-        <v>-5.0899017950146994E-2</v>
+        <v>-2.9904770000000001E-2</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>2.2847099931458701E-2</v>
+        <v>1.9484290000000001E-2</v>
       </c>
       <c r="B82">
-        <v>-5.4401625950146998E-2</v>
+        <v>-3.3739280000000003E-2</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>2.6362038420035101E-2</v>
+        <v>2.258949E-2</v>
       </c>
       <c r="B83">
-        <v>-5.7904234740022396E-2</v>
+        <v>-3.7573799999999997E-2</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>3.1634445999999997E-2</v>
+        <v>2.7432999999999999E-2</v>
       </c>
       <c r="B84">
-        <v>-6.1400665950146996E-2</v>
+        <v>-4.1587899999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>3.5149384999999998E-2</v>
+        <v>3.0538200000000001E-2</v>
       </c>
       <c r="B85">
-        <v>-6.4903273950147E-2</v>
+        <v>-4.5422410000000003E-2</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>4.0421792374340897E-2</v>
+        <v>3.5381700000000002E-2</v>
       </c>
       <c r="B86">
-        <v>-6.839970546315649E-2</v>
+        <v>-4.9436519999999998E-2</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>4.5694199999999997E-2</v>
+        <v>4.0225209999999997E-2</v>
       </c>
       <c r="B87">
-        <v>-7.1896136950146988E-2</v>
+        <v>-5.3450619999999997E-2</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>5.4481546328646699E-2</v>
+        <v>4.8545320000000003E-2</v>
       </c>
       <c r="B88">
-        <v>-7.5380212950146991E-2</v>
+        <v>-5.7823920000000001E-2</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>6.3268892550087802E-2</v>
+        <v>5.686542E-2</v>
       </c>
       <c r="B89">
-        <v>-7.8864288950146993E-2</v>
+        <v>-6.2197200000000001E-2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>7.0298769999999997E-2</v>
+        <v>6.3632939999999999E-2</v>
       </c>
       <c r="B90">
-        <v>-8.0597060950146987E-2</v>
+        <v>-6.4653240000000001E-2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>7.9086115999999998E-2</v>
+        <v>7.1953050000000005E-2</v>
       </c>
       <c r="B91">
-        <v>-8.408113695014699E-2</v>
+        <v>-6.9026539999999997E-2</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>8.6115993000000002E-2</v>
+        <v>7.872055E-2</v>
       </c>
       <c r="B92">
-        <v>-8.5813908950146997E-2</v>
+        <v>-7.1482569999999995E-2</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>9.6660808000000001E-2</v>
+        <v>8.8778969999999999E-2</v>
       </c>
       <c r="B93">
-        <v>-8.92918078678889E-2</v>
+        <v>-7.6035459999999999E-2</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>0.108963092901581</v>
+        <v>0.10076138</v>
       </c>
       <c r="B94">
-        <v>-9.1006047950146995E-2</v>
+        <v>-7.903027E-2</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>0.12302284685588699</v>
+        <v>0.11448211</v>
       </c>
       <c r="B95">
-        <v>-9.2714109681082901E-2</v>
+        <v>-8.2204680000000002E-2</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>0.13356766232161602</v>
+        <v>0.12472622</v>
       </c>
       <c r="B96">
-        <v>-9.4434526950146994E-2</v>
+        <v>-8.5019910000000004E-2</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>0.14762741627592202</v>
+        <v>0.13844695000000001</v>
       </c>
       <c r="B97">
-        <v>-9.6142588934372691E-2</v>
+        <v>-8.8194320000000007E-2</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>0.15817223174165201</v>
+        <v>0.14869106000000001</v>
       </c>
       <c r="B98">
-        <v>-9.7863006001113598E-2</v>
+        <v>-9.100954E-2</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>0.16871704720738101</v>
+        <v>0.15893518000000001</v>
       </c>
       <c r="B99">
-        <v>-9.9583423067854698E-2</v>
+        <v>-9.3824770000000002E-2</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>0.17926186267311001</v>
+        <v>0.16936498999999999</v>
       </c>
       <c r="B100">
-        <v>-9.9546358427278603E-2</v>
+        <v>-9.4902329999999993E-2</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>0.18980667813884</v>
+        <v>0.17979481</v>
       </c>
       <c r="B101">
-        <v>-9.9509293950147001E-2</v>
+        <v>-9.5979889999999998E-2</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>0.20035149360456903</v>
+        <v>0.19003892999999999</v>
       </c>
       <c r="B102">
-        <v>-0.1012297108534434</v>
+        <v>-9.8795110000000005E-2</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>0.21089630907029802</v>
+        <v>0.20046874000000001</v>
       </c>
       <c r="B103">
-        <v>-0.1011926462128673</v>
+        <v>-9.9872669999999997E-2</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>0.219683655291739</v>
+        <v>0.20916025999999999</v>
       </c>
       <c r="B104">
-        <v>-0.10116175895014699</v>
+        <v>-0.10077063999999999</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>0.23198594000175701</v>
+        <v>0.22132837999999999</v>
       </c>
       <c r="B105">
-        <v>-0.10111851695014699</v>
+        <v>-0.10202778999999999</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>0.244288224711775</v>
+        <v>0.23349650999999999</v>
       </c>
       <c r="B106">
-        <v>-0.101075274950147</v>
+        <v>-0.10328495</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>0.25659050942179201</v>
+        <v>0.24566462</v>
       </c>
       <c r="B107">
-        <v>-0.101032032950147</v>
+        <v>-0.10454210999999999</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>0.26713532500000003</v>
+        <v>0.25609443999999998</v>
       </c>
       <c r="B108">
-        <v>-0.10099496812979469</v>
+        <v>-0.10561966</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>0.277680140353251</v>
+        <v>0.26652426000000001</v>
       </c>
       <c r="B109">
-        <v>-0.1009579034892186</v>
+        <v>-0.10669723</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>0.28822495581898</v>
+        <v>0.27695407999999999</v>
       </c>
       <c r="B110">
-        <v>-0.1009208388486425</v>
+        <v>-0.10777478</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>0.30404217901757402</v>
+        <v>0.29259879999999999</v>
       </c>
       <c r="B111">
-        <v>-0.1008652418877784</v>
+        <v>-0.10939113</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>0.31810193297188</v>
+        <v>0.30669092999999997</v>
       </c>
       <c r="B112">
-        <v>-9.9058340950146997E-2</v>
+        <v>-0.10909021000000001</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>0.33040421768189804</v>
+        <v>0.31885904999999998</v>
       </c>
       <c r="B113">
-        <v>-9.9015098950146999E-2</v>
+        <v>-0.11034736000000001</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>0.34270650239191502</v>
+        <v>0.33121286999999999</v>
       </c>
       <c r="B114">
-        <v>-9.7214374791031705E-2</v>
+        <v>-0.10986686</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>0.35500878710193301</v>
+        <v>0.34338099999999999</v>
       </c>
       <c r="B115">
-        <v>-9.7171132710359598E-2</v>
+        <v>-0.11112402</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>0.36379613332337402</v>
+        <v>0.35225821000000002</v>
       </c>
       <c r="B116">
-        <v>-9.5382763802562498E-2</v>
+        <v>-0.11028432000000001</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>0.37434094878910301</v>
+        <v>0.36268802999999999</v>
       </c>
       <c r="B117">
-        <v>-9.5345698950146995E-2</v>
+        <v>-0.11136187</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>0.38312829501054402</v>
+        <v>0.37156525000000001</v>
       </c>
       <c r="B118">
-        <v>-9.3557329950146997E-2</v>
+        <v>-0.11052218</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>0.395430579720562</v>
+        <v>0.38373337000000002</v>
       </c>
       <c r="B119">
-        <v>-9.3514087950146998E-2</v>
+        <v>-0.11177933</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>0.40773286443057899</v>
+        <v>0.39608719999999997</v>
       </c>
       <c r="B120">
-        <v>-9.1713364385527893E-2</v>
+        <v>-0.11129883</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>0.42179261838488502</v>
+        <v>0.41017932000000001</v>
       </c>
       <c r="B121">
-        <v>-8.990646315744269E-2</v>
+        <v>-0.11099792</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>0.43409490309490301</v>
+        <v>0.42253313999999997</v>
       </c>
       <c r="B122">
-        <v>-8.8105739369453401E-2</v>
+        <v>-0.1105174</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>0.44815465704920904</v>
+        <v>0.43662527000000001</v>
       </c>
       <c r="B123">
-        <v>-8.6298838141368198E-2</v>
+        <v>-0.11021649</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>0.46045694175922602</v>
+        <v>0.44916478999999998</v>
       </c>
       <c r="B124">
-        <v>-8.2740632950146997E-2</v>
+        <v>-0.10799831999999999</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>0.47100175700000002</v>
+        <v>0.45959461000000001</v>
       </c>
       <c r="B125">
-        <v>-8.2703567950146994E-2</v>
+        <v>-0.10907588</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>0.48154657269068502</v>
+        <v>0.47021013</v>
       </c>
       <c r="B126">
-        <v>-8.0909021950146987E-2</v>
+        <v>-0.10841576999999999</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>0.49209138815641401</v>
+        <v>0.48082564999999999</v>
       </c>
       <c r="B127">
-        <v>-7.9114475309699506E-2</v>
+        <v>-0.10775568000000001</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>0.504393672866432</v>
+        <v>0.49317947000000001</v>
       </c>
       <c r="B128">
-        <v>-7.7313751950147003E-2</v>
+        <v>-0.10727515999999999</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>0.51845342682073792</v>
+        <v>0.50745731000000005</v>
       </c>
       <c r="B129">
-        <v>-7.3749368586307998E-2</v>
+        <v>-0.10523659</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>0.53075571153075496</v>
+        <v>0.51981113000000001</v>
       </c>
       <c r="B130">
-        <v>-7.1948644950146995E-2</v>
+        <v>-0.10475608</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>0.543057996240773</v>
+        <v>0.53235065999999998</v>
       </c>
       <c r="B131">
-        <v>-6.8390439303012598E-2</v>
+        <v>-0.10253791</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>0.55711775019507892</v>
+        <v>0.54644278000000002</v>
       </c>
       <c r="B132">
-        <v>-6.6583537950146987E-2</v>
+        <v>-0.10223699</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>0.57117750414938395</v>
+        <v>0.56072062</v>
       </c>
       <c r="B133">
-        <v>-6.3019154950146997E-2</v>
+        <v>-0.10019842</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>0.58699472734797797</v>
+        <v>0.57673673999999997</v>
       </c>
       <c r="B134">
-        <v>-5.9448594950146996E-2</v>
+        <v>-9.833944E-2</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>0.601054481302284</v>
+        <v>0.59082886999999995</v>
       </c>
       <c r="B135">
-        <v>-5.7641693950146997E-2</v>
+        <v>-9.8038520000000004E-2</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>0.61335676601230193</v>
+        <v>0.60336840000000003</v>
       </c>
       <c r="B136">
-        <v>-5.4083487950147002E-2</v>
+        <v>-9.5820349999999999E-2</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>0.62390158147803099</v>
+        <v>0.61398390999999997</v>
       </c>
       <c r="B137">
-        <v>-5.2288941950146994E-2</v>
+        <v>-9.5160239999999993E-2</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>0.63444639699999994</v>
+        <v>0.62478513999999996</v>
       </c>
       <c r="B138">
-        <v>-4.8736913950146996E-2</v>
+        <v>-9.2762490000000003E-2</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>0.64674868165377797</v>
+        <v>0.63713896000000003</v>
       </c>
       <c r="B139">
-        <v>-4.6936189950146992E-2</v>
+        <v>-9.2281970000000005E-2</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>0.6590509659999999</v>
+        <v>0.64967849</v>
       </c>
       <c r="B140">
-        <v>-4.3377983950146998E-2</v>
+        <v>-9.0063809999999994E-2</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>0.67135325107381294</v>
+        <v>0.66221801000000002</v>
       </c>
       <c r="B141">
-        <v>-3.9819778950147003E-2</v>
+        <v>-8.7845629999999994E-2</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>0.68189806653954299</v>
+        <v>0.67301924000000002</v>
       </c>
       <c r="B142">
-        <v>-3.626775095014699E-2</v>
+        <v>-8.544786E-2</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>0.6977152897381369</v>
+        <v>0.68903537000000004</v>
       </c>
       <c r="B143">
-        <v>-3.269718995014699E-2</v>
+        <v>-8.3588880000000004E-2</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>0.71353251293673092</v>
+        <v>0.70523720000000001</v>
       </c>
       <c r="B144">
-        <v>-2.7369147950146999E-2</v>
+        <v>-7.9992240000000006E-2</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>0.72759226689103595</v>
+        <v>0.71951503999999999</v>
       </c>
       <c r="B145">
-        <v>-2.3804764950146995E-2</v>
+        <v>-7.7953659999999994E-2</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>0.739894551601054</v>
+        <v>0.73186885999999995</v>
       </c>
       <c r="B146">
-        <v>-2.2004041950146991E-2</v>
+        <v>-7.7473150000000005E-2</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>0.75395430555535992</v>
+        <v>0.74633238999999996</v>
       </c>
       <c r="B147">
-        <v>-1.6682176979295998E-2</v>
+        <v>-7.3696910000000004E-2</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>0.76801405999999994</v>
+        <v>0.76079591999999996</v>
       </c>
       <c r="B148">
-        <v>-1.1360312336576001E-2</v>
+        <v>-6.9920679999999999E-2</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>0.78383128270825997</v>
+        <v>0.77699775000000004</v>
       </c>
       <c r="B149">
-        <v>-6.0322702537609907E-3</v>
+        <v>-6.6324019999999997E-2</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>0.79964850590685399</v>
+        <v>0.79319958999999995</v>
       </c>
       <c r="B150">
-        <v>-7.0422817094599466E-4</v>
+        <v>-6.2727379999999999E-2</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>0.81898066759402399</v>
+        <v>0.81287803000000003</v>
       </c>
       <c r="B151">
-        <v>4.6361687920620093E-3</v>
+        <v>-5.948991E-2</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>0.83831282899999993</v>
+        <v>0.83274216999999995</v>
       </c>
       <c r="B152">
-        <v>1.1734047462386002E-2</v>
+        <v>-5.4514800000000002E-2</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>0.857644990968365</v>
+        <v>0.85260630999999998</v>
       </c>
       <c r="B153">
-        <v>1.8831926132710994E-2</v>
+        <v>-4.9539680000000003E-2</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>0.87346221416695891</v>
+        <v>0.86899384999999996</v>
       </c>
       <c r="B154">
-        <v>2.5917449922842992E-2</v>
+        <v>-4.4205359999999999E-2</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>0.88927943736555293</v>
+        <v>0.88519568999999998</v>
       </c>
       <c r="B155">
-        <v>3.1245492005659001E-2</v>
+        <v>-4.0608720000000001E-2</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>0.90158172207557097</v>
+        <v>0.89792090999999996</v>
       </c>
       <c r="B156">
-        <v>3.6561179208282016E-2</v>
+        <v>-3.6652879999999999E-2</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>0.915641476029876</v>
+        <v>0.91257014999999997</v>
       </c>
       <c r="B157">
-        <v>4.3640525558318002E-2</v>
+        <v>-3.113898E-2</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>0.93321616847275901</v>
+        <v>0.93069599000000003</v>
       </c>
       <c r="B158">
-        <v>5.0732226788547011E-2</v>
+        <v>-2.598427E-2</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>0.94551845318277594</v>
+        <v>0.94360692000000002</v>
       </c>
       <c r="B159">
-        <v>5.7805395698487014E-2</v>
+        <v>-2.029077E-2</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>0.96133567638136996</v>
+        <v>0.95999445999999999</v>
       </c>
       <c r="B160">
-        <v>6.4890919488620011E-2</v>
+        <v>-1.495646E-2</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>0.97715289957996398</v>
+        <v>0.97656770000000004</v>
       </c>
       <c r="B161">
-        <v>7.3733924986068997E-2</v>
+        <v>-7.8844899999999992E-3</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>0.99121265353426991</v>
+        <v>0.99121693</v>
       </c>
       <c r="B162">
-        <v>8.081327133610601E-2</v>
+        <v>-2.3705800000000002E-3</v>
       </c>
     </row>
   </sheetData>

--- a/center_first_element_0deg.xlsx
+++ b/center_first_element_0deg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9709C6B-658E-45B6-B660-17AF00372306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC81FFC2-3E6A-4A8C-942C-940A9ADA4A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{934E2846-E07B-884A-9144-F9B94297545B}"/>
   </bookViews>
@@ -661,7 +661,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="162"/>
                 <c:pt idx="0">
-                  <c:v>1.0002798500000001</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.99928435999999998</c:v>
@@ -883,7 +883,7 @@
                   <c:v>7.8611000000000002E-4</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2.2900000000000001E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>1.4101999999999999E-3</c:v>
@@ -1144,7 +1144,7 @@
                   <c:v>0.97656770000000004</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.99121693</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1156,7 +1156,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="162"/>
                 <c:pt idx="0">
-                  <c:v>2.0677E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>7.3370199999999997E-3</c:v>
@@ -1378,7 +1378,7 @@
                   <c:v>5.0863499999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>-1.2663999999999999E-4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>-5.51922E-3</c:v>
@@ -1639,7 +1639,7 @@
                   <c:v>-7.8844899999999992E-3</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>-2.3705800000000002E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2807,10 +2807,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>1.0002798500000001</v>
+        <v>1</v>
       </c>
       <c r="B1">
-        <v>2.0677E-4</v>
+        <v>0</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>2.2900000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="B75">
-        <v>-1.2663999999999999E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -4098,10 +4098,10 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>0.99121693</v>
+        <v>1</v>
       </c>
       <c r="B162">
-        <v>-2.3705800000000002E-3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
